--- a/docs/StructureDefinition-RetinaDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-RetinaDiagnosticReport.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2405" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="505">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>DiagnosticReport for Retinascreening</t>
+    <t>Retina DiagnosticReport</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-08T17:39:22+01:00</t>
+    <t>2025-11-11T17:38:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,13 +84,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This report contains the results from a retina screening examination.</t>
+    <t>This diagnostic report for the grading of a retina screening examination.</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
-    <t>The purpose of RetinaIntegrationDiagnosticReport is to standardize the reporting of retina screening results, including AI analysis, to ensure consistent communication and interoperability between healthcare systems involved in diabetic retinopathy management.</t>
+    <t>The purpose of RetinaIntegrationDiagnosticReport is for a client to examine the state of a retina screening examination grading. This includes documenting which observations were made (e.g., fundus photography, OCT), any laboratory results relevant to the examination (e.g., HbA1c), and the results of AI analysis or manual grading for diabetic retinopathy (DR) and diabetic macular edema (DME). Additionally, it captures metadata about the examination, such as identifiers, image quality, and recommended follow-up actions.</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -472,7 +472,7 @@
     <t>Image Quality</t>
   </si>
   <si>
-    <t>A coded extension representing the quality of a diagnostic image</t>
+    <t>A coded extension representing the quality of a diagnostic image.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -489,7 +489,10 @@
 </t>
   </si>
   <si>
-    <t>KI Product Name extension</t>
+    <t>AI Product Name</t>
+  </si>
+  <si>
+    <t>Name of the AI product used for analysis.</t>
   </si>
   <si>
     <t>DiagnosticReport.extension:kiVersionAlgoritme</t>
@@ -502,7 +505,10 @@
 </t>
   </si>
   <si>
-    <t>KI versjon algoritme</t>
+    <t>AI Algorithm Version</t>
+  </si>
+  <si>
+    <t>Version of the AI algorithm used for analysis.</t>
   </si>
   <si>
     <t>DiagnosticReport.extension:kiFristNesteUndersokelse</t>
@@ -515,7 +521,10 @@
 </t>
   </si>
   <si>
-    <t>Frist neste undersøkelse</t>
+    <t>Deadline Next Examination</t>
+  </si>
+  <si>
+    <t>Number of days until next examination.</t>
   </si>
   <si>
     <t>DiagnosticReport.extension:kiProtokoll</t>
@@ -528,7 +537,10 @@
 </t>
   </si>
   <si>
-    <t>KI protokoll</t>
+    <t>AI Protocol</t>
+  </si>
+  <si>
+    <t>Protocol used by the AI solution for analysis.</t>
   </si>
   <si>
     <t>DiagnosticReport.extension:videreForlop</t>
@@ -541,10 +553,10 @@
 </t>
   </si>
   <si>
-    <t>Neste skritt i forløpet.</t>
-  </si>
-  <si>
-    <t>Angir videre forløp</t>
+    <t>Next Step</t>
+  </si>
+  <si>
+    <t>Next step in the grading process after photography. (4000-series)</t>
   </si>
   <si>
     <t>DiagnosticReport.extension:forrigeUndersokelse</t>
@@ -557,10 +569,10 @@
 </t>
   </si>
   <si>
-    <t>Titaksstaus forrige undersøkelse Retina</t>
-  </si>
-  <si>
-    <t>Angir om et tiltak er primært eller sekundært</t>
+    <t>Next Step Previous Examination</t>
+  </si>
+  <si>
+    <t>The next step in the screening process after the previous examination. (3000-series)</t>
   </si>
   <si>
     <t>DiagnosticReport.modifierExtension</t>
@@ -634,13 +646,10 @@
     <t>Sectra Study Identifier</t>
   </si>
   <si>
-    <t>Uniquely identify a study within the Sectra system, facilitating accurate tracking and retrieval of imaging data associated with retinascreening.</t>
-  </si>
-  <si>
-    <t>There may be multiple Sectra Study Identifiers if the report is associated with multiple imaging studies.</t>
-  </si>
-  <si>
-    <t>The Sectra Study Identifier is essential for linking the DiagnosticReport to the corresponding imaging study in the Sectra system.</t>
+    <t>Uniquely identify a study within the Sectra system.</t>
+  </si>
+  <si>
+    <t>There may be multiple Sectra Study Identifiers if the report is associated with multiple imaging studies. If there are no Sectra studies it is not possible for AI to grade the examination.</t>
   </si>
   <si>
     <t>DiagnosticReport.identifier:sectraStudyId.id</t>
@@ -875,7 +884,7 @@
     <t>Retina Examination Identifier</t>
   </si>
   <si>
-    <t>Identifier for the retina examination.</t>
+    <t>Identifies the retina examination in RetinaIntegration.</t>
   </si>
   <si>
     <t>DiagnosticReport.identifier:retinaExaminationId.id</t>
@@ -1011,7 +1020,19 @@
     <t>A code or name that describes this diagnostic report.</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/RetinaIntegration/ValueSet/diagnosticreport-codes-vs</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://ehelse.no/fhir/CodeSystem/no-kodeverk-8660"/&gt;
+    &lt;code value="B"/&gt;
+    &lt;display value="Bildediagnostikk"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Codes that describe Diagnostic Reports.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/report-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1279,7 +1300,7 @@
 </t>
   </si>
   <si>
-    <t>Optional Fundus Photography Observation</t>
+    <t>Optional Fundus Photography Observation.</t>
   </si>
   <si>
     <t>An optional observation indicating that fundus photography was performed.</t>
@@ -1912,7 +1933,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="85.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.03125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.3046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -3106,7 +3127,7 @@
         <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3186,13 +3207,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
@@ -3214,13 +3235,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3300,13 +3321,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>21</v>
@@ -3328,13 +3349,13 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3414,13 +3435,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>21</v>
@@ -3442,13 +3463,13 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3528,13 +3549,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>21</v>
@@ -3556,13 +3577,13 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3642,13 +3663,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>21</v>
@@ -3670,13 +3691,13 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3756,14 +3777,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3785,16 +3806,16 @@
         <v>136</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -3843,7 +3864,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3872,14 +3893,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3898,19 +3919,19 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3947,7 +3968,7 @@
         <v>21</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
@@ -3957,7 +3978,7 @@
         <v>140</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3972,30 +3993,30 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4014,19 +4035,19 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -4075,7 +4096,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4090,24 +4111,24 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4130,13 +4151,13 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4187,7 +4208,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4208,7 +4229,7 @@
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
@@ -4216,14 +4237,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4245,13 +4266,13 @@
         <v>136</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4292,7 +4313,7 @@
         <v>139</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
@@ -4301,7 +4322,7 @@
         <v>140</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4322,7 +4343,7 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
@@ -4330,10 +4351,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4359,16 +4380,16 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4393,13 +4414,13 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>21</v>
@@ -4417,7 +4438,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4438,7 +4459,7 @@
         <v>134</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4446,10 +4467,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4472,19 +4493,19 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4509,13 +4530,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4533,7 +4554,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4551,10 +4572,10 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
@@ -4562,10 +4583,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4591,16 +4612,16 @@
         <v>105</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4610,10 +4631,10 @@
         <v>21</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>21</v>
@@ -4649,7 +4670,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4667,10 +4688,10 @@
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
@@ -4678,10 +4699,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4704,16 +4725,16 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4727,7 +4748,7 @@
         <v>21</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>21</v>
@@ -4763,7 +4784,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4781,10 +4802,10 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
@@ -4792,10 +4813,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4818,13 +4839,13 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4875,7 +4896,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4893,10 +4914,10 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>21</v>
@@ -4904,10 +4925,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4930,16 +4951,16 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4989,7 +5010,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5007,10 +5028,10 @@
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>21</v>
@@ -5018,16 +5039,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5046,19 +5067,19 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5107,7 +5128,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5122,24 +5143,24 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5162,13 +5183,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5219,7 +5240,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5240,7 +5261,7 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
@@ -5248,14 +5269,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5277,13 +5298,13 @@
         <v>136</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5324,7 +5345,7 @@
         <v>139</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
@@ -5333,7 +5354,7 @@
         <v>140</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5354,7 +5375,7 @@
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
@@ -5362,10 +5383,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5391,16 +5412,16 @@
         <v>111</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5425,13 +5446,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5449,7 +5470,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5470,7 +5491,7 @@
         <v>134</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
@@ -5478,10 +5499,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5504,19 +5525,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5541,13 +5562,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5565,7 +5586,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5583,10 +5604,10 @@
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>21</v>
@@ -5594,10 +5615,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5623,16 +5644,16 @@
         <v>105</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5642,10 +5663,10 @@
         <v>21</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>21</v>
@@ -5681,7 +5702,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5699,10 +5720,10 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
@@ -5710,10 +5731,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5736,16 +5757,16 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5759,7 +5780,7 @@
         <v>21</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>21</v>
@@ -5795,7 +5816,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5813,10 +5834,10 @@
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
@@ -5824,10 +5845,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5850,13 +5871,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5907,7 +5928,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5925,10 +5946,10 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
@@ -5936,10 +5957,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5962,16 +5983,16 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6021,7 +6042,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6039,10 +6060,10 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
@@ -6050,14 +6071,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6076,19 +6097,19 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6137,7 +6158,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6152,13 +6173,13 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
@@ -6166,10 +6187,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6195,14 +6216,14 @@
         <v>111</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6227,13 +6248,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6251,7 +6272,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -6266,28 +6287,28 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6306,16 +6327,16 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6341,13 +6362,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6365,7 +6386,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6383,25 +6404,25 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6420,13 +6441,13 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6438,7 +6459,7 @@
         <v>21</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>21</v>
@@ -6453,11 +6474,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="Y40" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6475,7 +6498,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>91</v>
@@ -6490,28 +6513,28 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6530,17 +6553,17 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6589,7 +6612,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6604,28 +6627,28 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6644,19 +6667,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6705,7 +6728,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6720,28 +6743,28 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6760,19 +6783,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6821,7 +6844,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6836,28 +6859,28 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6876,19 +6899,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6937,7 +6960,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6955,25 +6978,25 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6992,19 +7015,19 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7053,7 +7076,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7068,28 +7091,28 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7108,19 +7131,19 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7169,7 +7192,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7184,24 +7207,24 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7224,19 +7247,19 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7285,7 +7308,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7303,10 +7326,10 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7314,14 +7337,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7340,19 +7363,19 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7389,7 +7412,7 @@
         <v>21</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
@@ -7399,7 +7422,7 @@
         <v>140</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7417,10 +7440,10 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7428,16 +7451,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7456,19 +7479,19 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7517,7 +7540,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7535,10 +7558,10 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7546,16 +7569,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7574,19 +7597,19 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7635,7 +7658,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7653,10 +7676,10 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7664,16 +7687,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7692,19 +7715,19 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7753,7 +7776,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7771,10 +7794,10 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -7782,16 +7805,16 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7810,19 +7833,19 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7871,7 +7894,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7889,10 +7912,10 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -7900,16 +7923,16 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7928,19 +7951,19 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7989,7 +8012,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8007,10 +8030,10 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8018,16 +8041,16 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8046,19 +8069,19 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8107,7 +8130,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8125,10 +8148,10 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8136,16 +8159,16 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8164,19 +8187,19 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8225,7 +8248,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8243,10 +8266,10 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8254,10 +8277,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8280,16 +8303,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8339,7 +8362,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8360,7 +8383,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8368,14 +8391,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8394,17 +8417,17 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8453,7 +8476,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8471,10 +8494,10 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8482,10 +8505,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8508,13 +8531,13 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8565,7 +8588,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8586,7 +8609,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8594,14 +8617,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8623,13 +8646,13 @@
         <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8679,7 +8702,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8700,7 +8723,7 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -8708,14 +8731,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8737,16 +8760,16 @@
         <v>136</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8795,7 +8818,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8824,10 +8847,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8850,19 +8873,19 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8911,7 +8934,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8932,7 +8955,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -8940,10 +8963,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8966,13 +8989,13 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9023,7 +9046,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>91</v>
@@ -9044,7 +9067,7 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9052,14 +9075,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9078,17 +9101,17 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9137,7 +9160,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9155,10 +9178,10 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -9166,10 +9189,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9192,13 +9215,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9225,11 +9248,11 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9247,7 +9270,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9265,10 +9288,10 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -9276,10 +9299,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9302,19 +9325,19 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9363,7 +9386,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9381,10 +9404,10 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>

--- a/docs/StructureDefinition-RetinaDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-RetinaDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T17:38:50+01:00</t>
+    <t>2025-11-12T18:21:01+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-RetinaDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-RetinaDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-12T18:21:01+01:00</t>
+    <t>2025-11-13T17:39:30+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -553,10 +553,10 @@
 </t>
   </si>
   <si>
-    <t>Next Step</t>
-  </si>
-  <si>
-    <t>Next step in the grading process after photography. (4000-series)</t>
+    <t>Grading Pending</t>
+  </si>
+  <si>
+    <t>Next step in grading this examination. (4000-series)</t>
   </si>
   <si>
     <t>DiagnosticReport.extension:forrigeUndersokelse</t>
@@ -569,7 +569,7 @@
 </t>
   </si>
   <si>
-    <t>Next Step Previous Examination</t>
+    <t>Next Examination Previous Examination</t>
   </si>
   <si>
     <t>The next step in the screening process after the previous examination. (3000-series)</t>

--- a/docs/StructureDefinition-RetinaDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-RetinaDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T17:38:50+01:00</t>
+    <t>2025-11-15T17:14:08+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -553,10 +553,10 @@
 </t>
   </si>
   <si>
-    <t>Next Step</t>
-  </si>
-  <si>
-    <t>Next step in the grading process after photography. (4000-series)</t>
+    <t>Grading Pending</t>
+  </si>
+  <si>
+    <t>Next step in grading this examination. (4000-series)</t>
   </si>
   <si>
     <t>DiagnosticReport.extension:forrigeUndersokelse</t>
@@ -569,7 +569,7 @@
 </t>
   </si>
   <si>
-    <t>Next Step Previous Examination</t>
+    <t>Next Examination Previous Examination</t>
   </si>
   <si>
     <t>The next step in the screening process after the previous examination. (3000-series)</t>

--- a/docs/StructureDefinition-RetinaDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-RetinaDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-15T17:14:08+01:00</t>
+    <t>2025-11-16T16:39:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3565,7 +3565,7 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
